--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -71,6 +71,9 @@
     <t xml:space="preserve">Velazquez</t>
   </si>
   <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
   </si>
   <si>
     <t xml:space="preserve">Jackson</t>
@@ -591,18 +597,18 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
         <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -613,7 +619,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -624,106 +630,106 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
         <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -734,211 +740,211 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
         <v>29</v>
-      </c>
-      <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
         <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
         <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -946,10 +952,10 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
@@ -957,32 +963,32 @@
         <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
@@ -990,10 +996,10 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -1001,10 +1007,10 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -1012,54 +1018,98 @@
         <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t xml:space="preserve">Royal Canin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barnes</t>
   </si>
   <si>
     <t xml:space="preserve">DOE v. CA</t>
@@ -820,7 +823,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C33" t="s">
         <v>32</v>
@@ -828,145 +831,145 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
         <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
         <v>36</v>
-      </c>
-      <c r="B41" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
@@ -974,10 +977,10 @@
         <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
@@ -985,131 +988,153 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
         <v>39</v>
-      </c>
-      <c r="B59" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cunningham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.A.R.P v. Trump</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
@@ -699,51 +702,51 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
         <v>25</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -754,87 +757,87 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
         <v>30</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
         <v>33</v>
@@ -842,156 +845,156 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
         <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
         <v>37</v>
-      </c>
-      <c r="B42" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
@@ -999,10 +1002,10 @@
         <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -1010,131 +1013,153 @@
         <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
         <v>40</v>
-      </c>
-      <c r="B61" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -50,6 +50,9 @@
     <t xml:space="preserve">Wisconsin Bell</t>
   </si>
   <si>
+    <t xml:space="preserve">Kouisisis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
@@ -102,6 +105,9 @@
   </si>
   <si>
     <t xml:space="preserve">Dewberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
   </si>
   <si>
     <t xml:space="preserve">Trump v. J.G.G.</t>
@@ -540,10 +546,10 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -551,7 +557,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -562,7 +568,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -573,7 +579,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -584,7 +590,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -595,7 +601,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -606,7 +612,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -614,18 +620,18 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -636,7 +642,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -647,117 +653,117 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
         <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -768,263 +774,263 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
         <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
         <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
         <v>38</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
@@ -1032,43 +1038,43 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
@@ -1082,7 +1088,7 @@
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -1093,7 +1099,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58">
@@ -1101,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -1123,10 +1129,10 @@
         <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
@@ -1134,32 +1140,98 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">Delligatti</t>
   </si>
   <si>
+    <t xml:space="preserve">BLOM Bank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
@@ -53,6 +56,15 @@
     <t xml:space="preserve">Kouisisis</t>
   </si>
   <si>
+    <t xml:space="preserve">Ames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith and Wesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
@@ -87,6 +99,9 @@
   </si>
   <si>
     <t xml:space="preserve">Wages and White Lion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC/Devas</t>
   </si>
   <si>
     <t xml:space="preserve">Cunningham</t>
@@ -535,10 +550,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +561,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -557,10 +572,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -568,10 +583,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -579,10 +594,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -590,10 +605,10 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +616,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -612,7 +627,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -623,7 +638,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -631,263 +646,263 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
         <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
         <v>36</v>
@@ -895,343 +910,464 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
         <v>37</v>
-      </c>
-      <c r="B39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>48</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>48</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -35,6 +35,9 @@
     <t xml:space="preserve">Thompson</t>
   </si>
   <si>
+    <t xml:space="preserve">A.J.T.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
     <t xml:space="preserve">BLOM Bank</t>
   </si>
   <si>
+    <t xml:space="preserve">Soto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
     <t xml:space="preserve">Seven County</t>
   </si>
   <si>
+    <t xml:space="preserve">Martin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trump v. J.G.G.</t>
   </si>
   <si>
@@ -149,6 +158,12 @@
     <t xml:space="preserve">Miller</t>
   </si>
   <si>
+    <t xml:space="preserve">Parrish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuch</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kavanaugh</t>
   </si>
   <si>
@@ -162,6 +177,9 @@
   </si>
   <si>
     <t xml:space="preserve">Bouarafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivers</t>
   </si>
 </sst>
 </file>
@@ -525,18 +543,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -547,7 +565,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -558,32 +576,32 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -591,10 +609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -602,10 +620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
@@ -613,464 +631,464 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
         <v>25</v>
-      </c>
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
         <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
         <v>38</v>
-      </c>
-      <c r="B41" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -1081,7 +1099,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
@@ -1089,10 +1107,10 @@
         <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
@@ -1100,7 +1118,7 @@
         <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
         <v>36</v>
@@ -1111,10 +1129,10 @@
         <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -1122,10 +1140,10 @@
         <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -1133,10 +1151,10 @@
         <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -1144,10 +1162,10 @@
         <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61">
@@ -1155,219 +1173,340 @@
         <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C77" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B79" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>53</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>53</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>53</v>
+      </c>
+      <c r="B82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>53</v>
+      </c>
+      <c r="B84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>53</v>
+      </c>
+      <c r="B85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>53</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>53</v>
+      </c>
+      <c r="B87" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" t="s">
         <v>48</v>
       </c>
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" t="s">
-        <v>47</v>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>53</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>53</v>
+      </c>
+      <c r="B89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>53</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>53</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -38,6 +38,15 @@
     <t xml:space="preserve">A.J.T.</t>
   </si>
   <si>
+    <t xml:space="preserve">Perttu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuld</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
@@ -53,6 +62,9 @@
     <t xml:space="preserve">Soto</t>
   </si>
   <si>
+    <t xml:space="preserve">Calumet </t>
+  </si>
+  <si>
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
@@ -71,6 +83,9 @@
     <t xml:space="preserve">Catholic Charities</t>
   </si>
   <si>
+    <t xml:space="preserve">Stanley</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
@@ -116,12 +131,18 @@
     <t xml:space="preserve">A.A.R.P v. Trump</t>
   </si>
   <si>
+    <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sotomayor</t>
   </si>
   <si>
     <t xml:space="preserve">Hungary</t>
   </si>
   <si>
+    <t xml:space="preserve">Parrish</t>
+  </si>
+  <si>
     <t xml:space="preserve">TikTok</t>
   </si>
   <si>
@@ -137,6 +158,9 @@
     <t xml:space="preserve">Trump v. J.G.G.</t>
   </si>
   <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kagan</t>
   </si>
   <si>
@@ -149,21 +173,27 @@
     <t xml:space="preserve">DOE v. CA</t>
   </si>
   <si>
+    <t xml:space="preserve">McLaughlin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gorsuch</t>
   </si>
   <si>
     <t xml:space="preserve">E.M.D. Sales</t>
   </si>
   <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
     <t xml:space="preserve">Miller</t>
   </si>
   <si>
-    <t xml:space="preserve">Parrish</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zuch</t>
   </si>
   <si>
+    <t xml:space="preserve">NRC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kavanaugh</t>
   </si>
   <si>
@@ -171,6 +201,9 @@
   </si>
   <si>
     <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R.J. Reynolds </t>
   </si>
   <si>
     <t xml:space="preserve">Jackson</t>
@@ -554,40 +587,40 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -598,54 +631,54 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -653,21 +686,21 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -675,10 +708,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -686,10 +719,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -697,406 +730,406 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
         <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
         <v>39</v>
@@ -1104,293 +1137,293 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B64" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B73" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
         <v>13</v>
-      </c>
-      <c r="C75" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B79" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
@@ -1401,112 +1434,431 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>60</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
         <v>53</v>
-      </c>
-      <c r="B85" t="s">
-        <v>13</v>
-      </c>
-      <c r="C85" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>61</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>61</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>61</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
         <v>19</v>
       </c>
-      <c r="C91" t="s">
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>61</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>61</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>61</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>61</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>61</v>
+      </c>
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>61</v>
+      </c>
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>61</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>61</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>64</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>64</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>64</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>64</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>64</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>64</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>64</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>64</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>64</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>64</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>64</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>64</v>
+      </c>
+      <c r="B114" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>64</v>
+      </c>
+      <c r="B116" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>64</v>
+      </c>
+      <c r="B117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>64</v>
+      </c>
+      <c r="B118" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>64</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>64</v>
+      </c>
+      <c r="B120" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -62,6 +62,9 @@
     <t xml:space="preserve">Soto</t>
   </si>
   <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calumet </t>
   </si>
   <si>
@@ -182,9 +185,6 @@
     <t xml:space="preserve">E.M.D. Sales</t>
   </si>
   <si>
-    <t xml:space="preserve">Oklahoma</t>
-  </si>
-  <si>
     <t xml:space="preserve">Miller</t>
   </si>
   <si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
   </si>
   <si>
     <t xml:space="preserve">Barrett</t>
@@ -678,10 +681,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
         <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -689,7 +692,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -700,7 +703,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -711,7 +714,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -722,7 +725,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -733,10 +736,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -744,10 +747,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -755,10 +758,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -766,10 +769,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -777,10 +780,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
         <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -788,7 +791,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -799,7 +802,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
@@ -810,7 +813,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
         <v>28</v>
@@ -821,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
@@ -832,7 +835,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
@@ -843,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -851,18 +854,18 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
         <v>32</v>
-      </c>
-      <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -873,7 +876,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
@@ -884,7 +887,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
@@ -895,76 +898,76 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
         <v>39</v>
@@ -972,65 +975,65 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
         <v>40</v>
-      </c>
-      <c r="B40" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C45" t="s">
         <v>43</v>
@@ -1038,10 +1041,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
         <v>44</v>
@@ -1049,238 +1052,238 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" t="s">
         <v>40</v>
-      </c>
-      <c r="B55" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
         <v>49</v>
-      </c>
-      <c r="B58" t="s">
-        <v>4</v>
-      </c>
-      <c r="C58" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s">
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>50</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
         <v>54</v>
-      </c>
-      <c r="B66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C66" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
@@ -1291,145 +1294,145 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82">
@@ -1440,7 +1443,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83">
@@ -1451,7 +1454,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84">
@@ -1462,7 +1465,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85">
@@ -1473,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86">
@@ -1481,10 +1484,10 @@
         <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C86" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87">
@@ -1492,10 +1495,10 @@
         <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88">
@@ -1503,10 +1506,10 @@
         <v>60</v>
       </c>
       <c r="B88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
@@ -1514,10 +1517,10 @@
         <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90">
@@ -1525,10 +1528,10 @@
         <v>60</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91">
@@ -1536,169 +1539,169 @@
         <v>60</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C93" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>60</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" t="s">
         <v>61</v>
-      </c>
-      <c r="B94" t="s">
-        <v>4</v>
-      </c>
-      <c r="C94" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B98" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B100" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C102" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C103" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B104" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B105" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
@@ -1709,156 +1712,200 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B107" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B108" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C110" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C112" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C113" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C115" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C116" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>65</v>
+      </c>
+      <c r="B120" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>65</v>
+      </c>
+      <c r="B121" t="s">
+        <v>25</v>
+      </c>
+      <c r="C121" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>65</v>
+      </c>
+      <c r="B122" t="s">
+        <v>25</v>
+      </c>
+      <c r="C122" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>65</v>
+      </c>
+      <c r="B123" t="s">
+        <v>25</v>
+      </c>
+      <c r="C123" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>65</v>
+      </c>
+      <c r="B124" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124" t="s">
         <v>64</v>
-      </c>
-      <c r="B120" t="s">
-        <v>24</v>
-      </c>
-      <c r="C120" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Wisconsin Bell</t>
   </si>
   <si>
-    <t xml:space="preserve">Kouisisis</t>
+    <t xml:space="preserve">Kousisis</t>
   </si>
   <si>
     <t xml:space="preserve">Ames</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Andrew</t>
   </si>
   <si>
-    <t xml:space="preserve">Willaims</t>
+    <t xml:space="preserve">Williams</t>
   </si>
   <si>
     <t xml:space="preserve">Glossip</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">Bouarafa</t>
+    <t xml:space="preserve">Bouarfa</t>
   </si>
   <si>
     <t xml:space="preserve">Rivers</t>
@@ -945,10 +945,10 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -959,7 +959,7 @@
         <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
@@ -970,7 +970,7 @@
         <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -981,18 +981,18 @@
         <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -1003,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -1014,7 +1014,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
@@ -1025,7 +1025,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
@@ -1044,10 +1044,10 @@
         <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
@@ -1058,7 +1058,7 @@
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
@@ -1069,7 +1069,7 @@
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -1080,7 +1080,7 @@
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -1091,7 +1091,7 @@
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -1102,7 +1102,7 @@
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -1113,7 +1113,7 @@
         <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -1124,7 +1124,7 @@
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1135,7 +1135,7 @@
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55">
@@ -1146,7 +1146,7 @@
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -1168,7 +1168,7 @@
         <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
@@ -1179,18 +1179,18 @@
         <v>25</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60">
@@ -1201,7 +1201,7 @@
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61">
@@ -1212,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -1223,7 +1223,7 @@
         <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
@@ -1234,7 +1234,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
@@ -1242,10 +1242,10 @@
         <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -1256,7 +1256,7 @@
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
@@ -1267,18 +1267,18 @@
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
@@ -1289,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
@@ -1300,7 +1300,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70">
@@ -1311,7 +1311,7 @@
         <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -1322,7 +1322,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72">
@@ -1330,10 +1330,10 @@
         <v>55</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
@@ -1344,7 +1344,7 @@
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74">
@@ -1355,7 +1355,7 @@
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75">
@@ -1366,7 +1366,7 @@
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
@@ -1374,10 +1374,10 @@
         <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
@@ -1388,7 +1388,7 @@
         <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -1399,7 +1399,7 @@
         <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79">
@@ -1410,7 +1410,7 @@
         <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80">
@@ -1421,7 +1421,7 @@
         <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81">
@@ -1432,18 +1432,18 @@
         <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B82" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83">
@@ -1454,7 +1454,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="84">
@@ -1465,7 +1465,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -1476,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86">
@@ -1487,7 +1487,7 @@
         <v>4</v>
       </c>
       <c r="C86" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87">
@@ -1498,7 +1498,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88">
@@ -1506,10 +1506,10 @@
         <v>60</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89">
@@ -1520,7 +1520,7 @@
         <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90">
@@ -1531,7 +1531,7 @@
         <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91">
@@ -1542,7 +1542,7 @@
         <v>18</v>
       </c>
       <c r="C91" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92">
@@ -1553,7 +1553,7 @@
         <v>18</v>
       </c>
       <c r="C92" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         <v>60</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94">
@@ -1575,18 +1575,18 @@
         <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B95" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96">
@@ -1597,7 +1597,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97">
@@ -1608,7 +1608,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98">
@@ -1619,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99">
@@ -1630,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100">
@@ -1641,7 +1641,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
@@ -1649,10 +1649,10 @@
         <v>62</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102">
@@ -1663,7 +1663,7 @@
         <v>18</v>
       </c>
       <c r="C102" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -1671,10 +1671,10 @@
         <v>62</v>
       </c>
       <c r="B103" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104">
@@ -1685,7 +1685,7 @@
         <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105">
@@ -1696,18 +1696,18 @@
         <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B106" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -1718,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108">
@@ -1729,7 +1729,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109">
@@ -1740,7 +1740,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110">
@@ -1748,10 +1748,10 @@
         <v>65</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111">
@@ -1762,7 +1762,7 @@
         <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
@@ -1773,7 +1773,7 @@
         <v>18</v>
       </c>
       <c r="C112" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113">
@@ -1784,7 +1784,7 @@
         <v>18</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
@@ -1795,7 +1795,7 @@
         <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115">
@@ -1806,7 +1806,7 @@
         <v>18</v>
       </c>
       <c r="C115" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116">
@@ -1817,7 +1817,7 @@
         <v>18</v>
       </c>
       <c r="C116" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
@@ -1825,10 +1825,10 @@
         <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118">
@@ -1836,10 +1836,10 @@
         <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119">
@@ -1850,7 +1850,7 @@
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
@@ -1861,7 +1861,7 @@
         <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121">
@@ -1872,7 +1872,7 @@
         <v>25</v>
       </c>
       <c r="C121" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="122">
@@ -1883,7 +1883,7 @@
         <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="123">
@@ -1894,7 +1894,7 @@
         <v>25</v>
       </c>
       <c r="C123" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="124">
@@ -1905,6 +1905,28 @@
         <v>25</v>
       </c>
       <c r="C124" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>65</v>
+      </c>
+      <c r="B125" t="s">
+        <v>25</v>
+      </c>
+      <c r="C125" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>65</v>
+      </c>
+      <c r="B126" t="s">
+        <v>25</v>
+      </c>
+      <c r="C126" t="s">
         <v>64</v>
       </c>
     </row>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -89,6 +89,12 @@
     <t xml:space="preserve">Stanley</t>
   </si>
   <si>
+    <t xml:space="preserve">Medina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
     <t xml:space="preserve">Feliciano</t>
   </si>
   <si>
+    <t xml:space="preserve">Guitierrez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
@@ -135,6 +144,9 @@
   </si>
   <si>
     <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hewitt</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
@@ -791,10 +803,10 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
         <v>25</v>
-      </c>
-      <c r="C23" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -802,10 +814,10 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -813,7 +825,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
         <v>28</v>
@@ -824,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
@@ -835,7 +847,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
@@ -846,7 +858,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -857,7 +869,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -865,40 +877,40 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
         <v>33</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -909,879 +921,879 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
         <v>41</v>
-      </c>
-      <c r="B50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>54</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
         <v>55</v>
-      </c>
-      <c r="B68" t="s">
-        <v>4</v>
-      </c>
-      <c r="C68" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C80" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
         <v>25</v>
-      </c>
-      <c r="C81" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B83" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B86" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B87" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C88" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
         <v>60</v>
-      </c>
-      <c r="B92" t="s">
-        <v>18</v>
-      </c>
-      <c r="C92" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B94" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C100" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B101" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B102" t="s">
         <v>18</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B103" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B104" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C104" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B111" t="s">
         <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B112" t="s">
         <v>18</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C113" t="s">
         <v>30</v>
@@ -1789,145 +1801,277 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C115" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B120" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B122" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C122" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C123" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B124" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C124" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B125" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C125" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B126" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>69</v>
+      </c>
+      <c r="B127" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>69</v>
+      </c>
+      <c r="B128" t="s">
+        <v>18</v>
+      </c>
+      <c r="C128" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>69</v>
+      </c>
+      <c r="B129" t="s">
+        <v>18</v>
+      </c>
+      <c r="C129" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>69</v>
+      </c>
+      <c r="B130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>69</v>
+      </c>
+      <c r="B131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>69</v>
+      </c>
+      <c r="B132" t="s">
+        <v>27</v>
+      </c>
+      <c r="C132" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>69</v>
+      </c>
+      <c r="B133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C133" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>69</v>
+      </c>
+      <c r="B134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C134" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>69</v>
+      </c>
+      <c r="B135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C135" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>69</v>
+      </c>
+      <c r="B136" t="s">
+        <v>27</v>
+      </c>
+      <c r="C136" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>69</v>
+      </c>
+      <c r="B137" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>69</v>
+      </c>
+      <c r="B138" t="s">
+        <v>27</v>
+      </c>
+      <c r="C138" t="s">
         <v>25</v>
-      </c>
-      <c r="C126" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -68,6 +68,9 @@
     <t xml:space="preserve">Calumet </t>
   </si>
   <si>
+    <t xml:space="preserve">Free Speech</t>
+  </si>
+  <si>
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
@@ -95,6 +98,12 @@
     <t xml:space="preserve">Riley</t>
   </si>
   <si>
+    <t xml:space="preserve">Trump v. CASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahmoud</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
@@ -122,6 +131,9 @@
     <t xml:space="preserve">Guitierrez</t>
   </si>
   <si>
+    <t xml:space="preserve">Kennedy</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
@@ -183,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">Barnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumers' Research</t>
   </si>
   <si>
     <t xml:space="preserve">DOE v. CA</t>
@@ -704,10 +719,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
         <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +730,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -726,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -737,7 +752,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -748,7 +763,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -759,10 +774,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -770,10 +785,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -781,10 +796,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -792,10 +807,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -803,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
@@ -814,7 +829,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -825,10 +840,10 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
         <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -836,10 +851,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -847,10 +862,10 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
@@ -858,7 +873,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -869,7 +884,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -880,7 +895,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -891,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
@@ -902,7 +917,7 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>35</v>
@@ -910,340 +925,340 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
         <v>36</v>
-      </c>
-      <c r="B33" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
         <v>45</v>
-      </c>
-      <c r="B56" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63" t="s">
         <v>43</v>
@@ -1251,310 +1266,310 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C65" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C67" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C69" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C70" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="s">
         <v>27</v>
-      </c>
-      <c r="C73" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C75" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>58</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
         <v>59</v>
-      </c>
-      <c r="B76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C76" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
       <c r="C78" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C82" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C83" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C84" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B85" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" t="s">
         <v>18</v>
-      </c>
-      <c r="C85" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C87" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92">
@@ -1562,10 +1577,10 @@
         <v>64</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93">
@@ -1573,10 +1588,10 @@
         <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94">
@@ -1584,10 +1599,10 @@
         <v>64</v>
       </c>
       <c r="B94" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95">
@@ -1595,10 +1610,10 @@
         <v>64</v>
       </c>
       <c r="B95" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
@@ -1606,10 +1621,10 @@
         <v>64</v>
       </c>
       <c r="B96" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -1617,10 +1632,10 @@
         <v>64</v>
       </c>
       <c r="B97" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98">
@@ -1628,10 +1643,10 @@
         <v>64</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C98" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1654,10 @@
         <v>64</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C99" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100">
@@ -1650,10 +1665,10 @@
         <v>64</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C100" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101">
@@ -1661,10 +1676,10 @@
         <v>64</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C101" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102">
@@ -1672,164 +1687,164 @@
         <v>64</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C102" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B110" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C110" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C111" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B112" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C112" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B113" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C113" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B114" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C114" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B115" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C115" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B116" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117">
@@ -1837,10 +1852,10 @@
         <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C117" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118">
@@ -1848,230 +1863,417 @@
         <v>69</v>
       </c>
       <c r="B118" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C118" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B122" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B124" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C126" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C127" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C128" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B129" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C129" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B130" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C130" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B131" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C131" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B132" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B133" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B134" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B135" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B136" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B137" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C137" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B138" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C138" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>74</v>
+      </c>
+      <c r="B139" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>74</v>
+      </c>
+      <c r="B140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>74</v>
+      </c>
+      <c r="B141" t="s">
+        <v>19</v>
+      </c>
+      <c r="C141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>74</v>
+      </c>
+      <c r="B142" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>74</v>
+      </c>
+      <c r="B143" t="s">
+        <v>19</v>
+      </c>
+      <c r="C143" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>74</v>
+      </c>
+      <c r="B144" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>74</v>
+      </c>
+      <c r="B145" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>74</v>
+      </c>
+      <c r="B146" t="s">
+        <v>30</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>74</v>
+      </c>
+      <c r="B147" t="s">
+        <v>30</v>
+      </c>
+      <c r="C147" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>74</v>
+      </c>
+      <c r="B148" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>74</v>
+      </c>
+      <c r="B149" t="s">
+        <v>30</v>
+      </c>
+      <c r="C149" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>74</v>
+      </c>
+      <c r="B150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>74</v>
+      </c>
+      <c r="B151" t="s">
+        <v>30</v>
+      </c>
+      <c r="C151" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>74</v>
+      </c>
+      <c r="B152" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>74</v>
+      </c>
+      <c r="B153" t="s">
+        <v>30</v>
+      </c>
+      <c r="C153" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>74</v>
+      </c>
+      <c r="B154" t="s">
+        <v>30</v>
+      </c>
+      <c r="C154" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>74</v>
+      </c>
+      <c r="B155" t="s">
+        <v>30</v>
+      </c>
+      <c r="C155" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
